--- a/config/_TableConfig/#Character.Adventurer-冒险者-1.xlsx
+++ b/config/_TableConfig/#Character.Adventurer-冒险者-1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="31050" windowHeight="11380"/>
+    <workbookView windowHeight="15120"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="108">
   <si>
     <t>##var</t>
   </si>
@@ -41,6 +41,9 @@
     <t>subrace</t>
   </si>
   <si>
+    <t>asset</t>
+  </si>
+  <si>
     <t>level</t>
   </si>
   <si>
@@ -77,6 +80,9 @@
     <t>int#ref=Character.TbRace</t>
   </si>
   <si>
+    <t>Character.Asset</t>
+  </si>
+  <si>
     <t>map,int#ref=Character.TbClasz,int</t>
   </si>
   <si>
@@ -92,6 +98,15 @@
     <t>map,(int#ref=Character.TbItem),float</t>
   </si>
   <si>
+    <t>prefab</t>
+  </si>
+  <si>
+    <t>squadPrefab</t>
+  </si>
+  <si>
+    <t>icon</t>
+  </si>
+  <si>
     <t>$type</t>
   </si>
   <si>
@@ -158,6 +173,15 @@
     <t>亚种</t>
   </si>
   <si>
+    <t>预制体</t>
+  </si>
+  <si>
+    <t>小队预制体</t>
+  </si>
+  <si>
+    <t>图标</t>
+  </si>
+  <si>
     <t>角色等级</t>
   </si>
   <si>
@@ -231,6 +255,12 @@
   </si>
   <si>
     <t>安缇洛雅·阿玛斯塔夏</t>
+  </si>
+  <si>
+    <t>adventurer</t>
+  </si>
+  <si>
+    <t>temp_icon</t>
   </si>
   <si>
     <t>圣武士</t>
@@ -337,7 +367,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -370,7 +400,7 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -378,14 +408,14 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -393,7 +423,7 @@
       <b/>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -401,7 +431,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -409,7 +439,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -417,7 +447,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -425,14 +455,14 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -440,7 +470,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -448,7 +478,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -456,14 +486,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -471,42 +501,42 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
@@ -705,7 +735,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="26">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -756,6 +786,153 @@
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -773,14 +950,36 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color rgb="FF7F7F7F"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -811,147 +1010,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1058,7 +1116,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="19" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1070,34 +1128,34 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="25" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="26" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1182,7 +1240,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1196,19 +1254,16 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="5" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1220,6 +1275,15 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1232,83 +1296,90 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="14" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="15" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="17" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="16" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="12" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="17" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="20" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="21" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="22" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="16" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Currency" xfId="2" builtinId="4"/>
-    <cellStyle name="Percent" xfId="3" builtinId="5"/>
-    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
-    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
-    <cellStyle name="Link" xfId="6" builtinId="8"/>
-    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
-    <cellStyle name="Note" xfId="8" builtinId="10"/>
-    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
-    <cellStyle name="Title" xfId="10" builtinId="15"/>
-    <cellStyle name="CExplanatory Text" xfId="11" builtinId="53"/>
-    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
-    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
-    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
-    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
-    <cellStyle name="Input" xfId="16" builtinId="20"/>
-    <cellStyle name="Output" xfId="17" builtinId="21"/>
-    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
-    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
-    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
-    <cellStyle name="Total" xfId="21" builtinId="25"/>
-    <cellStyle name="Good" xfId="22" builtinId="26"/>
-    <cellStyle name="Bad" xfId="23" builtinId="27"/>
-    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
-    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
-    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
-    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
-    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
-    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
-    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1577,17 +1648,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AS11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <dimension ref="A1:AV11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
     <col min="3" max="3" width="8.45454545454546" customWidth="1"/>
     <col min="4" max="4" width="21.2727272727273" customWidth="1"/>
-    <col min="5" max="5" width="13.2727272727273" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
-    <col min="27" max="27" width="7" customWidth="1"/>
+    <col min="5" max="5" width="24.1818181818182" customWidth="1"/>
+    <col min="6" max="8" width="13.2727272727273" customWidth="1"/>
+    <col min="15" max="15" width="18" customWidth="1"/>
+    <col min="30" max="30" width="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:45">
+    <row r="1" spans="1:48">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1601,29 +1673,31 @@
       <c r="E1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="5"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="M1" s="12"/>
-      <c r="N1" s="13"/>
-      <c r="O1" s="14" t="s">
+      <c r="O1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
+      <c r="P1" s="6"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -1633,68 +1707,73 @@
       <c r="Y1" s="1"/>
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
-      <c r="AB1" s="1" t="s">
-        <v>9</v>
-      </c>
+      <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
       <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
+      <c r="AE1" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="AF1" s="1"/>
       <c r="AG1" s="1"/>
-      <c r="AH1" s="1" t="s">
-        <v>10</v>
-      </c>
+      <c r="AH1" s="1"/>
       <c r="AI1" s="1"/>
       <c r="AJ1" s="1"/>
-      <c r="AK1" s="1"/>
+      <c r="AK1" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="AL1" s="1"/>
       <c r="AM1" s="1"/>
-      <c r="AN1" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="AN1" s="1"/>
       <c r="AO1" s="1"/>
       <c r="AP1" s="1"/>
-      <c r="AQ1" s="1"/>
+      <c r="AQ1" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="AR1" s="1"/>
       <c r="AS1" s="1"/>
+      <c r="AT1" s="1"/>
+      <c r="AU1" s="1"/>
+      <c r="AV1" s="1"/>
     </row>
-    <row r="2" spans="1:45">
+    <row r="2" spans="1:48">
       <c r="A2" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="5"/>
+      <c r="H2" s="3"/>
+      <c r="I2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="L2" s="15" t="s">
-        <v>17</v>
-      </c>
-      <c r="M2" s="16"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="14" t="s">
+      <c r="J2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O2" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="P2" s="10"/>
+      <c r="Q2" s="11"/>
+      <c r="R2" s="8" t="s">
+        <v>20</v>
+      </c>
       <c r="S2" s="1"/>
       <c r="T2" s="1"/>
       <c r="U2" s="1"/>
@@ -1704,76 +1783,85 @@
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1"/>
-      <c r="AB2" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
       <c r="AD2" s="1"/>
-      <c r="AE2" s="1"/>
+      <c r="AE2" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="AF2" s="1"/>
       <c r="AG2" s="1"/>
-      <c r="AH2" s="1" t="s">
-        <v>19</v>
-      </c>
+      <c r="AH2" s="1"/>
       <c r="AI2" s="1"/>
       <c r="AJ2" s="1"/>
-      <c r="AK2" s="1"/>
+      <c r="AK2" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="AL2" s="1"/>
       <c r="AM2" s="1"/>
-      <c r="AN2" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="AN2" s="1"/>
       <c r="AO2" s="1"/>
       <c r="AP2" s="1"/>
-      <c r="AQ2" s="1"/>
+      <c r="AQ2" s="1" t="s">
+        <v>22</v>
+      </c>
       <c r="AR2" s="1"/>
       <c r="AS2" s="1"/>
+      <c r="AT2" s="1"/>
+      <c r="AU2" s="1"/>
+      <c r="AV2" s="1"/>
     </row>
-    <row r="3" spans="1:45">
+    <row r="3" spans="1:48">
       <c r="A3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
+      <c r="F3" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H3" s="14" t="s">
+        <v>25</v>
+      </c>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
-      <c r="L3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3" s="18"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="P3" s="15"/>
+      <c r="Q3" s="16"/>
+      <c r="R3" s="8" t="s">
+        <v>27</v>
+      </c>
       <c r="S3" s="1"/>
       <c r="T3" s="1"/>
-      <c r="U3" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="V3" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="W3" s="1" t="s">
-        <v>25</v>
-      </c>
+      <c r="U3" s="1"/>
+      <c r="V3" s="1"/>
+      <c r="W3" s="1"/>
       <c r="X3" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="Z3" s="1"/>
-      <c r="AA3" s="1"/>
-      <c r="AB3" s="1"/>
+        <v>29</v>
+      </c>
+      <c r="Z3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA3" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AB3" s="1" t="s">
+        <v>32</v>
+      </c>
       <c r="AC3" s="1"/>
       <c r="AD3" s="1"/>
       <c r="AE3" s="1"/>
@@ -1791,855 +1879,926 @@
       <c r="AQ3" s="1"/>
       <c r="AR3" s="1"/>
       <c r="AS3" s="1"/>
+      <c r="AT3" s="1"/>
+      <c r="AU3" s="1"/>
+      <c r="AV3" s="1"/>
     </row>
-    <row r="4" spans="1:45">
+    <row r="4" spans="1:48">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
+      <c r="F4" s="12"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="14"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
-      <c r="M4" s="20"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="R4" s="1" t="s">
-        <v>31</v>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
+      <c r="P4" s="17"/>
+      <c r="Q4" s="18"/>
+      <c r="R4" s="8" t="s">
+        <v>33</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="U4" s="1"/>
-      <c r="V4" s="1"/>
-      <c r="W4" s="1"/>
+        <v>35</v>
+      </c>
+      <c r="U4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="X4" s="1"/>
       <c r="Y4" s="1"/>
       <c r="Z4" s="1"/>
       <c r="AA4" s="1"/>
-      <c r="AB4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AD4" s="1" t="s">
-        <v>36</v>
-      </c>
+      <c r="AB4" s="1"/>
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
       <c r="AE4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF4" s="1"/>
-      <c r="AG4" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="AF4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG4" s="1" t="s">
+        <v>41</v>
+      </c>
       <c r="AH4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AI4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AJ4" s="1" t="s">
-        <v>36</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
       <c r="AK4" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AL4" s="1"/>
-      <c r="AM4" s="1"/>
-      <c r="AN4" s="1"/>
+        <v>39</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM4" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>42</v>
+      </c>
       <c r="AO4" s="1"/>
       <c r="AP4" s="1"/>
       <c r="AQ4" s="1"/>
       <c r="AR4" s="1"/>
       <c r="AS4" s="1"/>
+      <c r="AT4" s="1"/>
+      <c r="AU4" s="1"/>
+      <c r="AV4" s="1"/>
     </row>
-    <row r="5" spans="1:45">
+    <row r="5" spans="1:48">
       <c r="A5" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
+      </c>
+      <c r="F5" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>50</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="14" t="s">
-        <v>49</v>
+        <v>53</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>55</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q5" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="R5" s="1" t="s">
-        <v>52</v>
+        <v>56</v>
+      </c>
+      <c r="Q5" s="1"/>
+      <c r="R5" s="8" t="s">
+        <v>57</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="Z5" s="1"/>
-      <c r="AA5" s="1"/>
+        <v>64</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AA5" s="1" t="s">
+        <v>66</v>
+      </c>
       <c r="AB5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AC5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD5" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="AC5" s="1"/>
+      <c r="AD5" s="1"/>
       <c r="AE5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AF5" s="1"/>
-      <c r="AG5" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG5" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="AH5" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="AI5" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="AJ5" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="AI5" s="1"/>
+      <c r="AJ5" s="1"/>
       <c r="AK5" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="AL5" s="1"/>
-      <c r="AM5" s="1"/>
+        <v>68</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="AM5" s="1" t="s">
+        <v>70</v>
+      </c>
       <c r="AN5" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="AO5" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="AP5" s="1" t="s">
-        <v>64</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="AO5" s="1"/>
+      <c r="AP5" s="1"/>
       <c r="AQ5" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="AR5" s="1" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="AS5" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>73</v>
       </c>
     </row>
-    <row r="6" spans="1:45">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6">
+    <row r="6" spans="1:48">
+      <c r="A6" s="19"/>
+      <c r="B6" s="20">
         <v>10001</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E6" s="6">
+      <c r="C6" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E6" s="20">
         <v>30005</v>
       </c>
-      <c r="F6" s="7">
-        <f t="shared" ref="F6:F11" si="0">H6+J6</f>
+      <c r="F6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I6" s="22">
+        <f t="shared" ref="I6:I11" si="0">K6+M6</f>
         <v>2</v>
       </c>
-      <c r="G6" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="8">
+      <c r="J6" s="22" t="s">
+        <v>78</v>
+      </c>
+      <c r="K6" s="23">
         <v>2</v>
       </c>
-      <c r="I6" s="8"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7">
+      <c r="L6" s="23"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22">
         <v>0</v>
       </c>
-      <c r="L6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="M6" s="22"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="23">
+      <c r="O6" s="22" t="s">
+        <v>79</v>
+      </c>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="22"/>
+      <c r="R6" s="25">
         <v>18</v>
       </c>
-      <c r="P6" s="24">
+      <c r="S6" s="26">
         <v>15</v>
       </c>
-      <c r="Q6" s="24">
+      <c r="T6" s="26">
         <v>16</v>
       </c>
-      <c r="R6" s="24">
+      <c r="U6" s="26">
         <v>12</v>
       </c>
-      <c r="S6" s="24">
+      <c r="V6" s="26">
         <v>14</v>
       </c>
-      <c r="T6" s="24">
+      <c r="W6" s="26">
         <v>17</v>
       </c>
-      <c r="U6" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="V6" s="28">
+      <c r="X6" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y6" s="27">
         <v>16</v>
       </c>
-      <c r="W6" s="28">
+      <c r="Z6" s="27">
         <v>6</v>
       </c>
-      <c r="X6" s="28">
+      <c r="AA6" s="27">
         <v>2</v>
       </c>
-      <c r="Y6" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z6" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="AA6" s="28"/>
-      <c r="AB6" s="30">
+      <c r="AB6" s="27" t="s">
+        <v>81</v>
+      </c>
+      <c r="AC6" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="AD6" s="27"/>
+      <c r="AE6" s="28">
         <v>42702</v>
       </c>
-      <c r="AC6" s="30">
+      <c r="AF6" s="28">
         <v>40501</v>
       </c>
-      <c r="AD6" s="30">
+      <c r="AG6" s="28">
         <v>40402</v>
       </c>
-      <c r="AE6" s="30"/>
-      <c r="AF6" s="30"/>
-      <c r="AG6" s="30"/>
-      <c r="AH6" s="30">
+      <c r="AH6" s="28"/>
+      <c r="AI6" s="28"/>
+      <c r="AJ6" s="28"/>
+      <c r="AK6" s="28">
         <v>0</v>
       </c>
-      <c r="AI6" s="30">
+      <c r="AL6" s="28">
         <v>0</v>
       </c>
-      <c r="AJ6" s="30">
+      <c r="AM6" s="28">
         <v>0</v>
       </c>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30"/>
-      <c r="AM6" s="30"/>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="32"/>
-      <c r="AP6" s="32"/>
-      <c r="AQ6" s="32"/>
-      <c r="AR6" s="32"/>
-      <c r="AS6" s="32"/>
+      <c r="AN6" s="28"/>
+      <c r="AO6" s="28"/>
+      <c r="AP6" s="28"/>
+      <c r="AQ6" s="29"/>
+      <c r="AR6" s="29"/>
+      <c r="AS6" s="29"/>
+      <c r="AT6" s="29"/>
+      <c r="AU6" s="29"/>
+      <c r="AV6" s="29"/>
     </row>
-    <row r="7" spans="1:45">
-      <c r="A7" s="5"/>
-      <c r="B7" s="9">
+    <row r="7" spans="1:48">
+      <c r="A7" s="19"/>
+      <c r="B7" s="30">
         <v>10002</v>
       </c>
-      <c r="C7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="C7" s="30" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="E7" s="30">
         <v>30003</v>
       </c>
-      <c r="F7" s="10">
+      <c r="F7" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I7" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G7" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="H7" s="10">
+      <c r="J7" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="K7" s="31">
         <v>2</v>
       </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="10"/>
-      <c r="K7" s="10">
+      <c r="L7" s="32"/>
+      <c r="M7" s="31"/>
+      <c r="N7" s="31">
         <v>0</v>
       </c>
-      <c r="L7" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M7" s="25"/>
-      <c r="N7" s="10"/>
-      <c r="O7" s="26">
+      <c r="O7" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="P7" s="33"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="34">
         <v>20</v>
       </c>
-      <c r="P7" s="27">
+      <c r="S7" s="35">
         <v>16</v>
       </c>
-      <c r="Q7" s="27">
+      <c r="T7" s="35">
         <v>17</v>
       </c>
-      <c r="R7" s="27">
+      <c r="U7" s="35">
         <v>8</v>
       </c>
-      <c r="S7" s="27">
+      <c r="V7" s="35">
         <v>11</v>
       </c>
-      <c r="T7" s="27">
+      <c r="W7" s="35">
         <v>14</v>
       </c>
-      <c r="U7" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="V7" s="29">
+      <c r="X7" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y7" s="36">
         <v>16</v>
       </c>
-      <c r="W7" s="29">
+      <c r="Z7" s="36">
         <v>5</v>
       </c>
-      <c r="X7" s="29">
+      <c r="AA7" s="36">
         <v>3</v>
       </c>
-      <c r="Y7" s="29" t="s">
+      <c r="AB7" s="36" t="s">
+        <v>86</v>
+      </c>
+      <c r="AC7" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="AD7" s="36">
+        <v>50503</v>
+      </c>
+      <c r="AE7" s="37">
+        <v>41901</v>
+      </c>
+      <c r="AF7" s="37">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="37">
+        <v>40402</v>
+      </c>
+      <c r="AH7" s="37"/>
+      <c r="AI7" s="37"/>
+      <c r="AJ7" s="37"/>
+      <c r="AK7" s="37">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="37">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="37">
+        <v>0</v>
+      </c>
+      <c r="AN7" s="37"/>
+      <c r="AO7" s="37"/>
+      <c r="AP7" s="37"/>
+      <c r="AQ7" s="29"/>
+      <c r="AR7" s="29"/>
+      <c r="AS7" s="29"/>
+      <c r="AT7" s="29"/>
+      <c r="AU7" s="29"/>
+      <c r="AV7" s="29"/>
+    </row>
+    <row r="8" spans="1:48">
+      <c r="A8" s="19"/>
+      <c r="B8" s="30">
+        <v>10003</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>88</v>
+      </c>
+      <c r="D8" s="30" t="s">
+        <v>89</v>
+      </c>
+      <c r="E8" s="30">
+        <v>30001</v>
+      </c>
+      <c r="F8" s="21" t="s">
         <v>76</v>
       </c>
-      <c r="Z7" s="29" t="s">
+      <c r="G8" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="AA7" s="29">
-        <v>50503</v>
-      </c>
-      <c r="AB7" s="31">
-        <v>41901</v>
-      </c>
-      <c r="AC7" s="31">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="31">
-        <v>40402</v>
-      </c>
-      <c r="AE7" s="31"/>
-      <c r="AF7" s="31"/>
-      <c r="AG7" s="31"/>
-      <c r="AH7" s="31">
-        <v>0</v>
-      </c>
-      <c r="AI7" s="31">
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="31">
-        <v>0</v>
-      </c>
-      <c r="AK7" s="31"/>
-      <c r="AL7" s="31"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="32"/>
-      <c r="AO7" s="32"/>
-      <c r="AP7" s="32"/>
-      <c r="AQ7" s="32"/>
-      <c r="AR7" s="32"/>
-      <c r="AS7" s="32"/>
-    </row>
-    <row r="8" spans="1:45">
-      <c r="A8" s="5"/>
-      <c r="B8" s="9">
-        <v>10003</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E8" s="9">
-        <v>30001</v>
-      </c>
-      <c r="F8" s="10">
+      <c r="I8" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G8" s="11" t="s">
+      <c r="J8" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="K8" s="31">
+        <v>2</v>
+      </c>
+      <c r="L8" s="32"/>
+      <c r="M8" s="31"/>
+      <c r="N8" s="31">
+        <v>0</v>
+      </c>
+      <c r="O8" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="34">
+        <v>16</v>
+      </c>
+      <c r="S8" s="35">
+        <v>16</v>
+      </c>
+      <c r="T8" s="35">
+        <v>14</v>
+      </c>
+      <c r="U8" s="35">
+        <v>12</v>
+      </c>
+      <c r="V8" s="35">
+        <v>14</v>
+      </c>
+      <c r="W8" s="35">
+        <v>12</v>
+      </c>
+      <c r="X8" s="36" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="10">
-        <v>2</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="10"/>
-      <c r="K8" s="10">
+      <c r="Y8" s="36">
+        <v>14</v>
+      </c>
+      <c r="Z8" s="36">
+        <v>6</v>
+      </c>
+      <c r="AA8" s="36">
+        <v>3</v>
+      </c>
+      <c r="AB8" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="AC8" s="36" t="s">
+        <v>92</v>
+      </c>
+      <c r="AD8" s="36"/>
+      <c r="AE8" s="37">
+        <v>42301</v>
+      </c>
+      <c r="AF8" s="37">
         <v>0</v>
       </c>
-      <c r="L8" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M8" s="25"/>
-      <c r="N8" s="10"/>
-      <c r="O8" s="26">
-        <v>16</v>
-      </c>
-      <c r="P8" s="27">
-        <v>16</v>
-      </c>
-      <c r="Q8" s="27">
-        <v>14</v>
-      </c>
-      <c r="R8" s="27">
-        <v>12</v>
-      </c>
-      <c r="S8" s="27">
-        <v>14</v>
-      </c>
-      <c r="T8" s="27">
-        <v>12</v>
-      </c>
-      <c r="U8" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="V8" s="29">
-        <v>14</v>
-      </c>
-      <c r="W8" s="29">
-        <v>6</v>
-      </c>
-      <c r="X8" s="29">
-        <v>3</v>
-      </c>
-      <c r="Y8" s="29" t="s">
-        <v>81</v>
-      </c>
-      <c r="Z8" s="29" t="s">
-        <v>82</v>
-      </c>
-      <c r="AA8" s="29"/>
-      <c r="AB8" s="31">
-        <v>42301</v>
-      </c>
-      <c r="AC8" s="31">
+      <c r="AG8" s="37">
+        <v>40202</v>
+      </c>
+      <c r="AH8" s="37"/>
+      <c r="AI8" s="37"/>
+      <c r="AJ8" s="37"/>
+      <c r="AK8" s="37">
+        <v>43001</v>
+      </c>
+      <c r="AL8" s="37">
         <v>0</v>
       </c>
-      <c r="AD8" s="31">
+      <c r="AM8" s="37">
         <v>40202</v>
       </c>
-      <c r="AE8" s="31"/>
-      <c r="AF8" s="31"/>
-      <c r="AG8" s="31"/>
-      <c r="AH8" s="31">
-        <v>43001</v>
-      </c>
-      <c r="AI8" s="31">
-        <v>0</v>
-      </c>
-      <c r="AJ8" s="31">
-        <v>40202</v>
-      </c>
-      <c r="AK8" s="31"/>
-      <c r="AL8" s="31"/>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="32"/>
-      <c r="AO8" s="32"/>
-      <c r="AP8" s="32"/>
-      <c r="AQ8" s="32"/>
-      <c r="AR8" s="32"/>
-      <c r="AS8" s="32"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="37"/>
+      <c r="AP8" s="37"/>
+      <c r="AQ8" s="29"/>
+      <c r="AR8" s="29"/>
+      <c r="AS8" s="29"/>
+      <c r="AT8" s="29"/>
+      <c r="AU8" s="29"/>
+      <c r="AV8" s="29"/>
     </row>
-    <row r="9" spans="1:45">
-      <c r="A9" s="5"/>
-      <c r="B9" s="9">
+    <row r="9" spans="1:48">
+      <c r="A9" s="19"/>
+      <c r="B9" s="30">
         <v>10004</v>
       </c>
-      <c r="C9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="C9" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="30">
         <v>30001</v>
       </c>
-      <c r="F9" s="10">
+      <c r="F9" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I9" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G9" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="H9" s="10">
+      <c r="J9" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="31">
         <v>2</v>
       </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="10"/>
-      <c r="K9" s="10">
+      <c r="L9" s="32"/>
+      <c r="M9" s="31"/>
+      <c r="N9" s="31">
         <v>0</v>
       </c>
-      <c r="L9" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M9" s="25"/>
-      <c r="N9" s="10"/>
-      <c r="O9" s="26">
+      <c r="O9" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="P9" s="33"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="34">
         <v>15</v>
       </c>
-      <c r="P9" s="27">
+      <c r="S9" s="35">
         <v>10</v>
       </c>
-      <c r="Q9" s="27">
+      <c r="T9" s="35">
         <v>14</v>
       </c>
-      <c r="R9" s="27">
+      <c r="U9" s="35">
         <v>12</v>
       </c>
-      <c r="S9" s="27">
+      <c r="V9" s="35">
         <v>18</v>
       </c>
-      <c r="T9" s="27">
+      <c r="W9" s="35">
         <v>12</v>
       </c>
-      <c r="U9" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="V9" s="29">
+      <c r="X9" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y9" s="36">
         <v>16</v>
       </c>
-      <c r="W9" s="29">
+      <c r="Z9" s="36">
         <v>6</v>
       </c>
-      <c r="X9" s="29">
+      <c r="AA9" s="36">
         <v>0</v>
       </c>
-      <c r="Y9" s="29" t="s">
-        <v>86</v>
-      </c>
-      <c r="Z9" s="29" t="s">
-        <v>87</v>
-      </c>
-      <c r="AA9" s="29">
+      <c r="AB9" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="AC9" s="36" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD9" s="36">
         <v>50303</v>
       </c>
-      <c r="AB9" s="31">
+      <c r="AE9" s="37">
         <v>40601</v>
       </c>
-      <c r="AC9" s="31">
+      <c r="AF9" s="37">
         <v>40501</v>
       </c>
-      <c r="AD9" s="31">
+      <c r="AG9" s="37">
         <v>40303</v>
       </c>
-      <c r="AE9" s="31"/>
-      <c r="AF9" s="31"/>
-      <c r="AG9" s="31"/>
-      <c r="AH9" s="31">
+      <c r="AH9" s="37"/>
+      <c r="AI9" s="37"/>
+      <c r="AJ9" s="37"/>
+      <c r="AK9" s="37">
         <v>0</v>
       </c>
-      <c r="AI9" s="31">
+      <c r="AL9" s="37">
         <v>0</v>
       </c>
-      <c r="AJ9" s="31">
+      <c r="AM9" s="37">
         <v>0</v>
       </c>
-      <c r="AK9" s="31"/>
-      <c r="AL9" s="31"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="32"/>
-      <c r="AO9" s="32"/>
-      <c r="AP9" s="32"/>
-      <c r="AQ9" s="32"/>
-      <c r="AR9" s="32"/>
-      <c r="AS9" s="32"/>
+      <c r="AN9" s="37"/>
+      <c r="AO9" s="37"/>
+      <c r="AP9" s="37"/>
+      <c r="AQ9" s="29"/>
+      <c r="AR9" s="29"/>
+      <c r="AS9" s="29"/>
+      <c r="AT9" s="29"/>
+      <c r="AU9" s="29"/>
+      <c r="AV9" s="29"/>
     </row>
-    <row r="10" spans="1:45">
-      <c r="A10" s="5"/>
-      <c r="B10" s="9">
+    <row r="10" spans="1:48">
+      <c r="A10" s="19"/>
+      <c r="B10" s="30">
         <v>10005</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>89</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="C10" s="30" t="s">
+        <v>98</v>
+      </c>
+      <c r="D10" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="E10" s="30">
         <v>30008</v>
       </c>
-      <c r="F10" s="10">
+      <c r="F10" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I10" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G10" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="H10" s="10">
+      <c r="J10" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="K10" s="31">
         <v>2</v>
       </c>
-      <c r="I10" s="11"/>
-      <c r="J10" s="10"/>
-      <c r="K10" s="10">
+      <c r="L10" s="32"/>
+      <c r="M10" s="31"/>
+      <c r="N10" s="31">
         <v>0</v>
       </c>
-      <c r="L10" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M10" s="25"/>
-      <c r="N10" s="10"/>
-      <c r="O10" s="26">
+      <c r="O10" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="P10" s="33"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="34">
         <v>10</v>
       </c>
-      <c r="P10" s="27">
+      <c r="S10" s="35">
         <v>18</v>
       </c>
-      <c r="Q10" s="27">
+      <c r="T10" s="35">
         <v>12</v>
       </c>
-      <c r="R10" s="27">
+      <c r="U10" s="35">
         <v>14</v>
       </c>
-      <c r="S10" s="27">
+      <c r="V10" s="35">
         <v>14</v>
       </c>
-      <c r="T10" s="27">
+      <c r="W10" s="35">
         <v>18</v>
       </c>
-      <c r="U10" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="V10" s="29">
+      <c r="X10" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y10" s="36">
         <v>15</v>
       </c>
-      <c r="W10" s="29">
+      <c r="Z10" s="36">
         <v>6</v>
       </c>
-      <c r="X10" s="29">
+      <c r="AA10" s="36">
         <v>4</v>
       </c>
-      <c r="Y10" s="29" t="s">
-        <v>91</v>
-      </c>
-      <c r="Z10" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="AA10" s="29">
+      <c r="AB10" s="36" t="s">
+        <v>101</v>
+      </c>
+      <c r="AC10" s="36" t="s">
+        <v>102</v>
+      </c>
+      <c r="AD10" s="36">
         <v>50203</v>
       </c>
-      <c r="AB10" s="31">
+      <c r="AE10" s="37">
         <v>40701</v>
       </c>
-      <c r="AC10" s="31">
+      <c r="AF10" s="37">
         <v>0</v>
       </c>
-      <c r="AD10" s="31">
+      <c r="AG10" s="37">
         <v>40202</v>
       </c>
-      <c r="AE10" s="31"/>
-      <c r="AF10" s="31"/>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="31">
+      <c r="AH10" s="37"/>
+      <c r="AI10" s="37"/>
+      <c r="AJ10" s="37"/>
+      <c r="AK10" s="37">
         <v>0</v>
       </c>
-      <c r="AI10" s="31">
+      <c r="AL10" s="37">
         <v>0</v>
       </c>
-      <c r="AJ10" s="31">
+      <c r="AM10" s="37">
         <v>0</v>
       </c>
-      <c r="AK10" s="31"/>
-      <c r="AL10" s="31"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="32"/>
-      <c r="AO10" s="32"/>
-      <c r="AP10" s="32"/>
-      <c r="AQ10" s="32"/>
-      <c r="AR10" s="32"/>
-      <c r="AS10" s="32"/>
+      <c r="AN10" s="37"/>
+      <c r="AO10" s="37"/>
+      <c r="AP10" s="37"/>
+      <c r="AQ10" s="29"/>
+      <c r="AR10" s="29"/>
+      <c r="AS10" s="29"/>
+      <c r="AT10" s="29"/>
+      <c r="AU10" s="29"/>
+      <c r="AV10" s="29"/>
     </row>
-    <row r="11" spans="1:45">
-      <c r="A11" s="5"/>
-      <c r="B11" s="9">
+    <row r="11" spans="1:48">
+      <c r="A11" s="19"/>
+      <c r="B11" s="30">
         <v>10006</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>94</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="C11" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="30">
         <v>30009</v>
       </c>
-      <c r="F11" s="10">
+      <c r="F11" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="31">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="G11" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="H11" s="10">
+      <c r="J11" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="K11" s="31">
         <v>2</v>
       </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="10"/>
-      <c r="K11" s="10">
+      <c r="L11" s="32"/>
+      <c r="M11" s="31"/>
+      <c r="N11" s="31">
         <v>0</v>
       </c>
-      <c r="L11" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="M11" s="25"/>
-      <c r="N11" s="10"/>
-      <c r="O11" s="26">
+      <c r="O11" s="31" t="s">
+        <v>79</v>
+      </c>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="34">
         <v>8</v>
       </c>
-      <c r="P11" s="27">
+      <c r="S11" s="35">
         <v>18</v>
       </c>
-      <c r="Q11" s="27">
+      <c r="T11" s="35">
         <v>16</v>
       </c>
-      <c r="R11" s="27">
+      <c r="U11" s="35">
         <v>11</v>
       </c>
-      <c r="S11" s="27">
+      <c r="V11" s="35">
         <v>12</v>
       </c>
-      <c r="T11" s="27">
+      <c r="W11" s="35">
         <v>18</v>
       </c>
-      <c r="U11" s="29" t="s">
-        <v>70</v>
-      </c>
-      <c r="V11" s="29">
+      <c r="X11" s="36" t="s">
+        <v>80</v>
+      </c>
+      <c r="Y11" s="36">
         <v>17</v>
       </c>
-      <c r="W11" s="29">
+      <c r="Z11" s="36">
         <v>6</v>
       </c>
-      <c r="X11" s="29">
+      <c r="AA11" s="36">
         <v>4</v>
       </c>
-      <c r="Y11" s="29" t="s">
-        <v>96</v>
-      </c>
-      <c r="Z11" s="29" t="s">
-        <v>97</v>
-      </c>
-      <c r="AA11" s="29">
+      <c r="AB11" s="36" t="s">
+        <v>106</v>
+      </c>
+      <c r="AC11" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="AD11" s="36">
         <v>51002</v>
       </c>
-      <c r="AB11" s="31">
+      <c r="AE11" s="37">
         <v>40701</v>
       </c>
-      <c r="AC11" s="31">
+      <c r="AF11" s="37">
         <v>0</v>
       </c>
-      <c r="AD11" s="31">
+      <c r="AG11" s="37">
         <v>40101</v>
       </c>
-      <c r="AE11" s="31"/>
-      <c r="AF11" s="31"/>
-      <c r="AG11" s="31"/>
-      <c r="AH11" s="31">
+      <c r="AH11" s="37"/>
+      <c r="AI11" s="37"/>
+      <c r="AJ11" s="37"/>
+      <c r="AK11" s="37">
         <v>0</v>
       </c>
-      <c r="AI11" s="31">
+      <c r="AL11" s="37">
         <v>0</v>
       </c>
-      <c r="AJ11" s="31">
+      <c r="AM11" s="37">
         <v>0</v>
       </c>
-      <c r="AK11" s="31"/>
-      <c r="AL11" s="31"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="32"/>
-      <c r="AO11" s="32"/>
-      <c r="AP11" s="32"/>
-      <c r="AQ11" s="32"/>
-      <c r="AR11" s="32"/>
-      <c r="AS11" s="32"/>
+      <c r="AN11" s="37"/>
+      <c r="AO11" s="37"/>
+      <c r="AP11" s="37"/>
+      <c r="AQ11" s="29"/>
+      <c r="AR11" s="29"/>
+      <c r="AS11" s="29"/>
+      <c r="AT11" s="29"/>
+      <c r="AU11" s="29"/>
+      <c r="AV11" s="29"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="28">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="L1:N1"/>
-    <mergeCell ref="O1:AA1"/>
-    <mergeCell ref="AB1:AG1"/>
-    <mergeCell ref="AH1:AM1"/>
-    <mergeCell ref="AN1:AS1"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="O1:Q1"/>
+    <mergeCell ref="R1:AD1"/>
+    <mergeCell ref="AE1:AJ1"/>
+    <mergeCell ref="AK1:AP1"/>
+    <mergeCell ref="AQ1:AV1"/>
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="G2:J2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="O2:AA2"/>
-    <mergeCell ref="AB2:AG2"/>
-    <mergeCell ref="AH2:AM2"/>
-    <mergeCell ref="AN2:AS2"/>
-    <mergeCell ref="O3:T3"/>
-    <mergeCell ref="Y3:AA3"/>
-    <mergeCell ref="AB3:AG3"/>
-    <mergeCell ref="AH3:AM3"/>
-    <mergeCell ref="AN3:AS3"/>
-    <mergeCell ref="Y4:AA4"/>
-    <mergeCell ref="AE4:AG4"/>
-    <mergeCell ref="AK4:AM4"/>
-    <mergeCell ref="M5:N5"/>
-    <mergeCell ref="Y5:AA5"/>
-    <mergeCell ref="AE5:AG5"/>
-    <mergeCell ref="AK5:AM5"/>
+    <mergeCell ref="F2:H2"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="R2:AD2"/>
+    <mergeCell ref="AE2:AJ2"/>
+    <mergeCell ref="AK2:AP2"/>
+    <mergeCell ref="AQ2:AV2"/>
+    <mergeCell ref="R3:W3"/>
+    <mergeCell ref="AB3:AD3"/>
+    <mergeCell ref="AE3:AJ3"/>
+    <mergeCell ref="AK3:AP3"/>
+    <mergeCell ref="AQ3:AV3"/>
+    <mergeCell ref="AB4:AD4"/>
+    <mergeCell ref="AH4:AJ4"/>
+    <mergeCell ref="AN4:AP4"/>
+    <mergeCell ref="P5:Q5"/>
+    <mergeCell ref="AB5:AD5"/>
+    <mergeCell ref="AH5:AJ5"/>
+    <mergeCell ref="AN5:AP5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
